--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -325,6 +325,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:academicDegree</t>
   </si>
   <si>
@@ -369,9 +372,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:academicDegree.value[x]</t>
@@ -1219,24 +1219,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>91</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1261,10 +1261,10 @@
         <v>93</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1324,7 +1324,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>83</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1438,10 +1438,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1470,7 +1470,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1530,7 +1530,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>83</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1567,16 +1567,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1626,7 +1626,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>85</v>
@@ -1641,7 +1641,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
@@ -1736,13 +1736,13 @@
         <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -1781,7 +1781,7 @@
         <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1841,7 +1841,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>83</v>
@@ -1855,7 +1855,7 @@
         <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1958,7 +1958,7 @@
         <v>130</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1987,7 +1987,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2047,7 +2047,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>83</v>
@@ -2061,7 +2061,7 @@
         <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2084,16 +2084,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2143,7 +2143,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>85</v>
@@ -2158,7 +2158,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2253,13 +2253,13 @@
         <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -2298,7 +2298,7 @@
         <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2358,7 +2358,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>83</v>
@@ -2372,7 +2372,7 @@
         <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2475,7 +2475,7 @@
         <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2504,7 +2504,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2564,7 +2564,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>83</v>
@@ -2578,7 +2578,7 @@
         <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2601,16 +2601,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2660,7 +2660,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>85</v>
@@ -2675,7 +2675,7 @@
         <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19">
@@ -2770,21 +2770,21 @@
         <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2807,16 +2807,16 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2866,7 +2866,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -2881,7 +2881,7 @@
         <v>76</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -2978,13 +2978,13 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
